--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O396"/>
+  <dimension ref="A1:O413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30081,52 +30081,1359 @@
           <t>05/09/2026 a las 09:58</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr">
+      <c r="F396" t="n">
+        <v>28</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>I. E. OLAYA</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>I. E. LLANADAS</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>CORREG. LLANADAS</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>ón: CRA. 11 10-14</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:14</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BLANQUITA DEL MURRI</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BLANQUITA DEL MURRI - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>CORREG. LA BLANQUITA MURRI</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>ón: CORREG. LA BLANQUITA MURRI</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:14</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>Occidente</t>
-        </is>
-      </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I396" t="inlineStr">
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
         <is>
           <t>ía de Educación: Antioquia</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>I. E. OLAYA</t>
-        </is>
-      </c>
-      <c r="K396" t="inlineStr">
-        <is>
-          <t>I. E. LLANADAS</t>
-        </is>
-      </c>
-      <c r="L396" t="inlineStr">
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>I. E. R. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>COLEGIO PUEBLO NUEVO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
         <is>
           <t>RURAL</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>CORREG. LLANADAS</t>
-        </is>
-      </c>
-      <c r="N396" t="inlineStr">
-        <is>
-          <t>ón: CRA. 11 10-14</t>
-        </is>
-      </c>
-      <c r="O396" t="inlineStr">
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>CORREG.PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:14</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>I.E. SANTA TERESITA</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>E U SANTA TERESITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>ón: CLL 19 CRA 6 A 8-6</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:14</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>I.E.R. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>I.E.R MELLOVILLAVICENCIO -SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>CORREG. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>ón: CORREG. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:16</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>C.E.R CUTURU MEDIO</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Dirección: VDA CUTURU MEDIO</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>ón: VDA CUTURU MEDIO</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:16</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PAULINA</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>C. E. R. LA BARCA CAUTIVA</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>VDA. PTO. RAUDAL</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>ón: VDA PTO. RAUDAL</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:16</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>I. E. MONSENOR J. IVAN CADAVID GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>COLEGIO SIMON BOLIVAR - MONSENOR J. IVAN SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>BARRIO. INDICIO</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>ón: CL. 25 Nº 29-41</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>C.E.R. SAN PABLO</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>ón: VEREDA SAN PABLO</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>I. E. LUIS LOPEZ DE MESA</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BRAMADORA</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>VDA. GUADALUPE IV</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>ón: VDA GUADALUPE IV</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BLANQUITA DEL MURRI</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>C. E. R. ALTO DE MURRI</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>CORREG DE MURRI</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>ón: CORREG DE MURRI</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>I.E.R. SAN PABLO APOSTOL</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN PABLO APOSTOL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>VDA. EL CAIMAN</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL CAIMÁN</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>I. E. R. GUADUAL ARRIBA</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>I. E. R. GUADUAL ARRIBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>CORREG. GUADUAL ARRIBA</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>ón: CORREG. GUADUAL ARRIBA</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Vigia Del Fuerte</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Vigia del Fuerte</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>I. E. R. ALIANZA PARA EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>C. E. R. ISLETA</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>VDA. ISLETA</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>ón: VDA ISLETA</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>I. E. R. SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>COLEGIO SANTA CATALINA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>CORREG. SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SANTA CATALINA.</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>I. E. COLOMBIA</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>COLEGIO COLOMBIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>B. GAITAN</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>ón: CL. 83 CRA67</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>I. E. LA ESMERALDA</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>COLEGIO LA ESMERALDA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>BARRIO LA ESMERALDA</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>ón: KR 38 69 B 75</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>El Santuario</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:18</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>C. E. R. JOSE IGNACIO BOTERO PALACIO</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>C. E. R. JOSE IGNACIO BOTERO PALACIO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>VDA. VALLE DE MARIA</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>ón: VDA. VALLE DE MARIA</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O413"/>
+  <dimension ref="A1:O417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30156,10 +30156,8 @@
           <t>10/09/2026 a las 09:14</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F397" t="n">
+        <v>23</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -30233,10 +30231,8 @@
           <t>10/09/2026 a las 09:14</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F398" t="n">
+        <v>28</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -30310,10 +30306,8 @@
           <t>10/09/2026 a las 09:14</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F399" t="n">
+        <v>15</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -30387,10 +30381,8 @@
           <t>10/09/2026 a las 09:14</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="F400" t="n">
+        <v>24</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -30464,10 +30456,8 @@
           <t>10/09/2026 a las 09:16</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F401" t="n">
+        <v>20</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -30541,10 +30531,8 @@
           <t>10/09/2026 a las 09:16</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="F402" t="n">
+        <v>27</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -30618,10 +30606,8 @@
           <t>10/09/2026 a las 09:16</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F403" t="n">
+        <v>14</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -30695,10 +30681,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="F404" t="n">
+        <v>31</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -30772,10 +30756,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="F405" t="n">
+        <v>25</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -30849,10 +30831,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="F406" t="n">
+        <v>26</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -30926,10 +30906,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F407" t="n">
+        <v>18</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -31003,10 +30981,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F408" t="n">
+        <v>11</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -31080,10 +31056,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F409" t="n">
+        <v>14</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -31157,10 +31131,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F410" t="n">
+        <v>7</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -31234,10 +31206,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="F411" t="n">
+        <v>29</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -31311,10 +31281,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="F412" t="n">
+        <v>26</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -31388,10 +31356,8 @@
           <t>10/09/2026 a las 09:18</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="F413" t="n">
+        <v>51</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -31434,6 +31400,314 @@
         </is>
       </c>
       <c r="O413" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:16</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>C. E. R. TINITACITA</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>C.E.R EL CHISPERO</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Dirección: VDA EL CHISPERO</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>ón: VDA EL CHISPERO</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>I. E. GASPAR DE RODAS</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>LICEO GASPAR DE RODAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>CORRREG. JARDIN</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>ón: SALIDA A MANIZALES KM1</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:17</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>I. E. LLANO DE CORDOBA</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>I. E. LLANO DE CORDOBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>KR 18 9 271</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>ón: KR 18 9 271</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>10/09/2026 a las 09:18</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>I. E. R. LA JOSEFINA</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>I. E. R. LA JOSEFINA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>VDA. LA JOSEFINA</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA JOSEFINA</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O417"/>
+  <dimension ref="A1:O418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31431,10 +31431,8 @@
           <t>10/09/2026 a las 09:16</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="F414" t="n">
+        <v>45</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -31508,10 +31506,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F415" t="n">
+        <v>14</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -31585,10 +31581,8 @@
           <t>10/09/2026 a las 09:17</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="F416" t="n">
+        <v>36</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -31662,10 +31656,8 @@
           <t>10/09/2026 a las 09:18</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="F417" t="n">
+        <v>29</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
@@ -31708,6 +31700,83 @@
         </is>
       </c>
       <c r="O417" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>12/09/2026 a las 16:00</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>INST EDUC RODRIGO ARENAS BETANCUR</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>INST EDUC RODRIGO ARENAS BETANCUR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Dirección: IND CL 81 94AA - 15</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>ón: IND CL 81 94AA - 15</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O418"/>
+  <dimension ref="A1:O422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31731,10 +31731,8 @@
           <t>12/09/2026 a las 16:00</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="F418" t="n">
+        <v>60</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -31777,6 +31775,314 @@
         </is>
       </c>
       <c r="O418" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>16/09/2026 a las 10:46</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>I.E. Nuevo Antioquia</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Sede Alto Mantecas</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Dirección: VDA ALTO MANTECA</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>ón: VDA ALTO MANTECA</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>16/09/2026 a las 12:16</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>SEDE MARIA CAMILA RENDON RENDON - LA LAJA</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>VDA. LA LAJA</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>ón: K. 35 AUTOP.MED-BOG.</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>16/09/2026 a las 12:19</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>I. E. GILBERTO ECHEVERRI MEJIA</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>I. E. GILBERTO ECHEVERRI MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>LLANO GRANDE</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>ón: VDA. CABECERAS</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>16/09/2026 a las 12:22</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>INST EDUC CEFA</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>INST EDUC CEFA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>BOSTON</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>ón: CL 50 41 55</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O422"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31806,10 +31806,8 @@
           <t>16/09/2026 a las 10:46</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="F419" t="n">
+        <v>70</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -31883,10 +31881,8 @@
           <t>16/09/2026 a las 12:16</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="F420" t="n">
+        <v>38</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -31960,10 +31956,8 @@
           <t>16/09/2026 a las 12:19</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="F421" t="n">
+        <v>38</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
@@ -32037,10 +32031,8 @@
           <t>16/09/2026 a las 12:22</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F422" t="n">
+        <v>28</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -32083,6 +32075,1623 @@
         </is>
       </c>
       <c r="O422" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>I. E. SANTA RITA</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>I. E. SANTA RITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>CORREG SANTA RITA</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SANTA RITA</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>I. E. MARIANO DE JESUS EUSSE</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>I. E. R. CHOCHO LA LOMA</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>VDA. CHOCHO LOMA</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>ón: VDA CHOCHO LOMA</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Anza</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>I. E. R. ASCENSION MONTOYA DE TORRES</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>E R CHUSCALITA</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>VDA CHUSCALITA</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>ón: VDA CHUSCALITA</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>I. E. R. EL HATO</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>C. E. R. SOLEDAD</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>VDA LA SOLEDAD</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA SOLEDAD</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>San Andrés De Cuerquia</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquia</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>I. E. R. LAS CRUCES</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>C. E. R. EL VERGEL</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>VDA. EL VERGEL</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>ón: VDA EL VERGEL</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>I. E. JESUS MARIA VALLE JARAMILLO</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>C. E. R. LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>VDA. CANDELARIA BAJA</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>ón: VDA. CANDELARIA BAJA</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>C. E. R. MORRON</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>C. E. R. OREJON</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>VDA. OREJON</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>ón: VDA. OREJON</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Don Matías</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Don Matías</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>I. E. R. BENILDA VALENCIA</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>I. E. R. BENILDA VALENCIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>VDA. LAS ANIMAS</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>ón: VDA. LAS ANIMAS</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>C. E. R. LAS CRUCES</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>VDA. LAS AURAS</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>ón: VDA. LAS AURAS</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>I. E. SANTO DOMINGO SAVIO</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>SANTA LAURA</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Dirección: VDA SANTA LAURA</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>ón: VDA SANTA LAURA</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>I. E. JHON F. KENNEDY</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>I. E. R. JOSE MARIA CORDOBA</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>VDA EL PESCADO</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL PESCADO</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>I. E. JHON F. KENNEDY</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>C. E. R. ATANASIO GIRARDOT</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>VDA. MATA BAJA</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>ón: VDA. MATA BAJA</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>I. E. ANORI</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>LICEO JESUS MARIA URREA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>BARRIO. LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>ón: KR 35 26 380</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>I. E. RAFAEL NUNEZ</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>LICEO RAFAEL NUNEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>B. VILLA DEL LAGO</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>ón: CL 28 28 18</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Educación artística - artes escénicas</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:56</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>I. E. JESUS MARIA ROJAS PAGOLA</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>I. E. JESUS MARIA ROJAS PAGOLA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>BOYACA</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>ón: KR BOYACA 49 A 42</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Puerto Berrío</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:57</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Puerto Berrio</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CARLOTA</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>C. E. R. ALTO BUENOS AIRES</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>VDA. ALTO DE BUENOS AIRES</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>ón: VDA ALTO DE BUENOS AIRES</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:57</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CRUZADA</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>COLEGIO LA CRUZADA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>CORREG. LA CRUZADA</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>ón: CORREG.LA CRUZADA</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:57</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>I. E. CUTURU</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>I. E. CUTURU - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>CORREG.CUTURU</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>ón: CORREG.CUTURU</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:57</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>I. E. J. EMILIO VALDERRAMA AGUDELO</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>I. E. J. EMILIO VALDERRAMA AGUDELO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>KR 10 12 07</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>ón: KR 10 12 07</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 11:57</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>I. E. R. BUCHADO MEDIO</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>I. E. R. BUCHADO MEDIO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>VDA. QUEBRADA DEL MEDIO</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>ón: VEREDA QUEBRADA DEL MEDIO</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>19/09/2026 a las 12:05</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>INST EDUC LA AVANZADA</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>INST EDUC LA AVANZADA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Dirección: IND CR 27 NO 106BB-61</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>ón: IND CR 27 NO 106BB-61</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32106,10 +32106,8 @@
           <t>19/09/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F423" t="n">
+        <v>7</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -32183,10 +32181,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F424" t="n">
+        <v>8</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
@@ -32260,10 +32256,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F425" t="n">
+        <v>9</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -32337,10 +32331,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F426" t="n">
+        <v>11</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
@@ -32414,10 +32406,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F427" t="n">
+        <v>8</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -32491,10 +32481,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F428" t="n">
+        <v>13</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -32568,10 +32556,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F429" t="n">
+        <v>8</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -32645,10 +32631,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F430" t="n">
+        <v>12</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -32722,10 +32706,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F431" t="n">
+        <v>15</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -32799,10 +32781,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F432" t="n">
+        <v>6</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -32876,10 +32856,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F433" t="n">
+        <v>7</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -32953,10 +32931,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F434" t="n">
+        <v>5</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -33030,10 +33006,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F435" t="n">
+        <v>10</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -33107,10 +33081,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F436" t="n">
+        <v>6</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -33184,10 +33156,8 @@
           <t>19/09/2026 a las 11:56</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F437" t="n">
+        <v>5</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -33261,10 +33231,8 @@
           <t>19/09/2026 a las 11:57</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F438" t="n">
+        <v>6</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -33338,10 +33306,8 @@
           <t>19/09/2026 a las 11:57</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F439" t="n">
+        <v>11</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -33415,10 +33381,8 @@
           <t>19/09/2026 a las 11:57</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F440" t="n">
+        <v>2</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -33492,10 +33456,8 @@
           <t>19/09/2026 a las 11:57</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F441" t="n">
+        <v>6</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -33569,10 +33531,8 @@
           <t>19/09/2026 a las 11:57</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F442" t="n">
+        <v>4</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -33646,10 +33606,8 @@
           <t>19/09/2026 a las 12:05</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F443" t="n">
+        <v>19</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -33692,6 +33650,237 @@
         </is>
       </c>
       <c r="O443" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>24/09/2026 a las 11:42</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>INST EDUC JOSE ASUNCION SILVA</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>INST EDUC JOSE ASUNCION SILVA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Dirección: IND CLL 118 NO 64CC-68</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>ón: IND CLL 118 NO 64CC-68</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>24/09/2026 a las 11:42</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>INST EDUC VILLA DEL SOCORRO</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>INST EDUC VILLA DEL SOCORRO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Dirección: CL 104 C 48 50</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>ón: CL 104 C 48 50</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>24/09/2026 a las 11:42</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>INST EDUC BARRIO OLAYA HERRERA</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>INST EDUC BARRIO OLAYA HERRERA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Dirección: KR 101 C 58 44</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>ón: KR 101 C 58 44</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O446"/>
+  <dimension ref="A1:O447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33681,10 +33681,8 @@
           <t>24/09/2026 a las 11:42</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F444" t="n">
+        <v>10</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -33758,10 +33756,8 @@
           <t>24/09/2026 a las 11:42</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F445" t="n">
+        <v>12</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
@@ -33835,10 +33831,8 @@
           <t>24/09/2026 a las 11:42</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F446" t="n">
+        <v>8</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -33881,6 +33875,83 @@
         </is>
       </c>
       <c r="O446" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>24/09/2026 a las 11:46</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>I.E. Sagrado Corazon de Jesus</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>I.E. Sagrado Corazon de Jesus - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Dirección: CR 16 X CL 101</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>ón: CR 16 X CL 101</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33906,10 +33906,8 @@
           <t>24/09/2026 a las 11:46</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="F447" t="n">
+        <v>26</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -33952,6 +33950,160 @@
         </is>
       </c>
       <c r="O447" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>29/09/2026 a las 10:13</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>SEDE MARIA CAMILA RENDON RENDON - LA LAJA</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>VDA. LA LAJA</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>ón: K. 35 AUTOP.MED-BOG.</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>29/09/2026 a las 10:14</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>I. E. GILBERTO ECHEVERRI MEJIA</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>I. E. GILBERTO ECHEVERRI MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>LLANO GRANDE</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>ón: VDA. CABECERAS</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O449"/>
+  <dimension ref="A1:O450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33981,10 +33981,8 @@
           <t>29/09/2026 a las 10:13</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="F448" t="n">
+        <v>113</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -34058,10 +34056,8 @@
           <t>29/09/2026 a las 10:14</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="F449" t="n">
+        <v>118</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -34104,6 +34100,83 @@
         </is>
       </c>
       <c r="O449" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>01/10/2026 a las 13:59</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>I. E. GILBERTO ECHEVERRI MEJIA</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>I. E. GILBERTO ECHEVERRI MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>LLANO GRANDE</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>ón: VDA. CABECERAS</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O450"/>
+  <dimension ref="A1:O455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34131,10 +34131,8 @@
           <t>01/10/2026 a las 13:59</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="F450" t="n">
+        <v>70</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -34177,6 +34175,391 @@
         </is>
       </c>
       <c r="O450" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>02/10/2026 a las 08:50</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>SEDE MARIA CAMILA RENDON RENDON - LA LAJA</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>VDA. LA LAJA</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>ón: K. 35 AUTOP.MED-BOG.</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>02/10/2026 a las 10:38</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>INST EDUC JAVIERA LONDO</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>INST EDUC JAVIERA LONDO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 53 NO 40-65</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>ón: CLL 53 NO 40-65</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>02/10/2026 a las 10:38</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>INST EDUC LA PIEDAD</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>INST EDUC LA PIEDAD - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Dirección: CR 81 NO 54-71</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>ón: CR 81 NO 54-71</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>02/10/2026 a las 11:39</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>INST EDUC CARLOS VIECO ORTIZ</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>SEC ESC JUAN DE DIOS ARANZAZU</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>ón: CL 42 105 42</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>02/10/2026 a las 11:39</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>INST EDUC JESUS REY</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>INST EDUC JESUS REY - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Dirección: CR 88 NO 77A-11</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>ón: CR 88 NO 77A-11</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O455"/>
+  <dimension ref="A1:O466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34206,10 +34206,8 @@
           <t>02/10/2026 a las 08:50</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="F451" t="n">
+        <v>136</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -34283,10 +34281,8 @@
           <t>02/10/2026 a las 10:38</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="F452" t="n">
+        <v>47</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -34360,10 +34356,8 @@
           <t>02/10/2026 a las 10:38</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="F453" t="n">
+        <v>52</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -34437,10 +34431,8 @@
           <t>02/10/2026 a las 11:39</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="F454" t="n">
+        <v>54</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -34514,10 +34506,8 @@
           <t>02/10/2026 a las 11:39</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="F455" t="n">
+        <v>57</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -34560,6 +34550,853 @@
         </is>
       </c>
       <c r="O455" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>I. E. EL BAGRE</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>LICEO EL BAGRE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Dirección: CL 48 54 A 20</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>ón: CL 48 54 A 20</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>I. E. LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>E U I SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>CABECERA MPAL.</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>ón: CR. 9 CON CL. 18</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>I. E. JORGE ELIECER GAITAN</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>COLEGIO JORGE ELIECER GAITAN - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>ón: CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>I. E. JORGE ELIECER GAITAN</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>COLEGIO JORGE ELIECER GAITAN - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>ón: CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>C.E.R. SAN PABLO</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>ón: VEREDA SAN PABLO</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>I. E. GASPAR DE RODAS</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>LICEO GASPAR DE RODAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>CORRREG. JARDIN</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>ón: SALIDA A MANIZALES KM1</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>C. E. R. LA LINDA</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>I. E. R. SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>VDA. STO. DOMINGO</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>ón: VDA. STO. DOMINGO</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR PRESBITERO JOSE GOMEZ ISAZA</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR PRESBITERO JOSE GOMEZ ISAZA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>VDA GUAYABAL</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>ón: IND VDA RIO ARRIBA SECTOR GUAYABAL</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>I. E. R. TULAPITA</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>I. E. R. TULAPITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>VDA. TULAPITA</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>ón: VDA. TULAPITA</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>I. E. SAN PEDRO DE URABA</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>LICEO SAN PEDRO DE URABA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>CAMILO TORRES</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>ón: CL 52 A 47 70</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>C. E. R. EL CARMIN</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>VDA. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O466"/>
+  <dimension ref="A1:O467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34581,10 +34581,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F456" t="n">
+        <v>5</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -34658,10 +34656,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F457" t="n">
+        <v>2</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -34735,10 +34731,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F458" t="n">
+        <v>4</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -34812,10 +34806,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F459" t="n">
+        <v>1</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -34889,10 +34881,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F460" t="n">
+        <v>3</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -34966,10 +34956,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F461" t="n">
+        <v>4</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -35043,10 +35031,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F462" t="n">
+        <v>1</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -35120,10 +35106,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F463" t="n">
+        <v>1</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
@@ -35197,10 +35181,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F464" t="n">
+        <v>1</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -35274,10 +35256,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F465" t="n">
+        <v>3</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
@@ -35351,10 +35331,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F466" t="n">
+        <v>3</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
@@ -35397,6 +35375,83 @@
         </is>
       </c>
       <c r="O466" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>06/10/2026 a las 16:25</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>I. E. JHON F. KENNEDY</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>C. E. R. JORGE ROBLEDO ORTIZ</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>VDA. EL JABON</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL JABON</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O467"/>
+  <dimension ref="A1:O470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35406,10 +35406,8 @@
           <t>06/10/2026 a las 16:25</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="F467" t="n">
+        <v>44</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -35452,6 +35450,237 @@
         </is>
       </c>
       <c r="O467" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>07/10/2026 a las 10:16</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>ía de Educación: Sabaneta</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>I. E. RAFAEL J. MEJIA</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>COLEGIO RAFAEL J. MEJIA</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>CAÑAVIEJO</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>ón: CR 45 77CS 47</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>07/10/2026 a las 10:21</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>ía de Educación: La Estrella</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>B. BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>ón: KR 63 77 S 105</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>07/10/2026 a las 10:35</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>INST EDUC PERPETUO SOCORRO</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>INST EDUC PERPETUO SOCORRO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>Dirección: CR 92 NO 34D-53</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>ón: CR 92 NO 34D-53</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O470"/>
+  <dimension ref="A1:O471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35481,10 +35481,8 @@
           <t>07/10/2026 a las 10:16</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="F468" t="n">
+        <v>55</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -35558,10 +35556,8 @@
           <t>07/10/2026 a las 10:21</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="F469" t="n">
+        <v>59</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -35635,10 +35631,8 @@
           <t>07/10/2026 a las 10:35</t>
         </is>
       </c>
-      <c r="F470" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="F470" t="n">
+        <v>63</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -35681,6 +35675,83 @@
         </is>
       </c>
       <c r="O470" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>09/10/2026 a las 16:32</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>ía de Educación: La Estrella</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>B. BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>ón: KR 63 77 S 105</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O471"/>
+  <dimension ref="A1:O481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35706,10 +35706,8 @@
           <t>09/10/2026 a las 16:32</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="F471" t="n">
+        <v>46</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -35752,6 +35750,776 @@
         </is>
       </c>
       <c r="O471" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>I. E. SAN PEDRO DE URABA</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>LICEO SAN PEDRO DE URABA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>CAMILO TORRES</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>ón: CL 52 A 47 70</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>I.E.R. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>CENTRO EDUCATIVO RURAL SANTA ROSA DE LOS PALMARES</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Dirección: VDA SANTA ROSA DE LOS PALMANRES</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>ón: VDA SANTA ROSA DE LOS PALMANRES</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>I. E. SAN PIO X</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>C. E. R SAN LUIS DEL CAFE</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>VDA SAN LUIS DEL CAFE</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>ón: VDA. SAN LUIS DEL CAFE</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>I. E. SAN JOSE DEL CITARA</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>LICEO SAN JOSE DEL CITARA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>B. UNICO</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>ón: KR 47 B 46 A 139</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>I.E.R. MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>I.E.R. MONTENEGRO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>CORREG BARRO BLANCO</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>ón: CORREG. BARRO BLANCO</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>C.E.R. SAN PABLO</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>ón: VEREDA SAN PABLO</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>BARRIO. EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>ón: KR 45 50 52</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>BARRIO. EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>ón: KR 45 50 52</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:08</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>ía de Educación: La Estrella</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>B. BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>ón: KR 63 77 S 105</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>15/10/2026 a las 15:40</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>I. E. COMERCIAL DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>SEDE ESCUELA PIO XII</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Dirección: CARRERA 31 N0 38 SUR 51</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>ón: CARRERA 31 N0 38 SUR 51</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O481"/>
+  <dimension ref="A1:O482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35781,10 +35781,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="F472" t="n">
+        <v>74</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -35858,10 +35856,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="F473" t="n">
+        <v>92</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
@@ -35935,10 +35931,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F474" t="n">
+        <v>28</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
@@ -36012,10 +36006,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="F475" t="n">
+        <v>43</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -36089,10 +36081,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="F476" t="n">
+        <v>24</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
@@ -36166,10 +36156,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="F477" t="n">
+        <v>72</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -36243,10 +36231,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="F478" t="n">
+        <v>27</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -36320,10 +36306,8 @@
           <t>15/10/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="F479" t="n">
+        <v>30</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -36397,10 +36381,8 @@
           <t>15/10/2026 a las 15:08</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="F480" t="n">
+        <v>85</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -36474,10 +36456,8 @@
           <t>15/10/2026 a las 15:40</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="F481" t="n">
+        <v>127</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -36520,6 +36500,83 @@
         </is>
       </c>
       <c r="O481" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>16/10/2026 a las 14:26</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>ía de Educación: Sabaneta</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>I. E. RAFAEL J. MEJIA</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>COLEGIO RAFAEL J. MEJIA</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>CAÑAVIEJO</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>ón: CR 45 77CS 47</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O482"/>
+  <dimension ref="A1:O484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36531,10 +36531,8 @@
           <t>16/10/2026 a las 14:26</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="F482" t="n">
+        <v>27</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -36577,6 +36575,160 @@
         </is>
       </c>
       <c r="O482" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>16/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>INST EDUC KENNEDY</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>INST EDUC KENNEDY - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Dirección: KR 76 92 199</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>ón: KR 76 92 199</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>16/10/2026 a las 16:11</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>ía de Educación: Sabaneta</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>I. E. JOSE FELIX DE RESTREPO VELEZ</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>I. E. JOSE FELIX DE RESTREPO VELEZ</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>BARRIO. SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>ón: CRA. 46 B 76 S-17</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O484"/>
+  <dimension ref="A1:O508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36606,10 +36606,8 @@
           <t>16/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="F483" t="n">
+        <v>46</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -36683,10 +36681,8 @@
           <t>16/10/2026 a las 16:11</t>
         </is>
       </c>
-      <c r="F484" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="F484" t="n">
+        <v>31</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -36729,6 +36725,1854 @@
         </is>
       </c>
       <c r="O484" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>I. E. R. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>CENTRO EDUCATIVO RURAL BRISAS DEL RIO</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Dirección: VDA BRISAS DEL RIO</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>ón: VDA BRISAS DEL RIO</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Caracolí</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Caracolí</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>I. E. GABRIEL CORREA VELEZ</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>I. E. GABRIEL CORREA VELEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>PALANQUERO</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>ón: CLL 22 21B-10</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>I. E. FEDERICO ANGEL</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>I. E. FEDERICO ANGEL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>CABECERA MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>ón: CL 132 S 44 93</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>I. E. R. GRANIZADA</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>I. E. R. GRANIZADA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>GRANIZAL</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>ón: CARRETERA VIEJA A GUARNE KM 8</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>I. E. CARLOS ARTURO DUQUE RAMIREZ</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>COLEGIO CARLOS ARTURO DUQUE RAMIREZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>BARRIO HECTOR DUQUE</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>ón: KR 5 44 77</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>I. E. CUTURU</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>I. E. CUTURU - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>CORREG.CUTURU</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>ón: CORREG.CUTURU</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>I.E.R TRINIDAD ARRIBA</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>C. E. R. SAN PEDRO ABAJO</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>VDA SAN PEDRO ABAJO</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>ón: VDA. SAN PEDRO ABAJO</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>I. E. LICEO CAUCASIA</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>LICEO CAUCASIA 1A. AGRUPACION - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>LA YE</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>ón: CR 20 TRONCAL DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>I. E. GASPAR DE RODAS</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>LICEO GASPAR DE RODAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>CORRREG. JARDIN</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>ón: SALIDA A MANIZALES KM1</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>C. E. R. TINITACITA</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>C. E. R. LOS TOROS</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>VDA. LOS TOROS</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>ón: VDA LOS TOROS</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>COLEGIO LIBORIO BATALLER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>BARRIO GUANANA</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>ón: KR 55 47 65</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>I. E. SANTO DOMINGO SAVIO</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>C.E.R. MONTEFRIO ALTO</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>VDA. MONTEFRÍO ALTO</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>ón: VDA. MONTEFRÍO ALTO</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>I.E. IGNACIO YEPES YEPES</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>LICEO IGNACIO YEPES YEPES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>ALTO DE LAS TAPIAS</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>ón: CQ 8 15 149</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>COLEGIO LIBORIO BATALLER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>BARRIO GUANANA</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>ón: KR 55 47 65</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:06</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>I. E. SAN PIO X</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>C. E. R RUBICON</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>VDA. RUBICON</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>ón: VDA. RUBICON</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Anza</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>C. E. R. LA CEJITA</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>C. E. R. LA CEJITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>VDA. LA CEJITA</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA CEJITA</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>I. E. PRESBITERO GABRIEL YEPES YEPES</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>I. E. PRESBITERO GABRIEL YEPES YEPES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>CORREG. SEVILLA</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>ón: CRA 6 12-3</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>I. E. R. BUCHADO MEDIO</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>I. E. R. ALTO ROSARIO</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. ALTOS DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>ón: VDA. ALTOS DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Chigorodó</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Chigorodó</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>I. E. MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>I. E. MARIA AUXILIADORA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>BR LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>ón: KR 111 93 35</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>I. E. R. OVEJAS</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>I. E. R. OVEJAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>CORREG. OVEJAS</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>ón: CORREG. OVEJAS</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>I. E. R. PUERTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>COLEGIO PUERTO LOPEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>CORREGIMIENTO PUERTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUERTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>I. E. R. EL CARMELO</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>COLEGIO EL CARMELO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>CORREG. EL CARMELO</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>ón: CORREG. EL CARMELO</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>I. E. R. NOBOGACITA</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>C. E. R. SAN MATEO</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>VDA. SAN MATEO</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>ón: VDA SAN MATEO</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>22/10/2026 a las 13:14</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>INST EDUC FINCA LA MESA</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>INST EDUC FINCA LA MESA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>EL PLAYON DE LOS COMUNEROS</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>ón: CL 118 51 A 03</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O508"/>
+  <dimension ref="A1:O510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36756,10 +36756,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="F485" t="n">
+        <v>22</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -36833,10 +36831,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F486" t="n">
+        <v>11</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -36910,10 +36906,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F487" t="n">
+        <v>13</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -36987,10 +36981,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F488" t="n">
+        <v>28</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -37064,10 +37056,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F489" t="n">
+        <v>11</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -37141,10 +37131,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F490" t="n">
+        <v>10</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -37218,10 +37206,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F491" t="n">
+        <v>7</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
@@ -37295,10 +37281,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F492" t="n">
+        <v>8</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
@@ -37372,10 +37356,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F493" t="n">
+        <v>7</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -37449,10 +37431,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F494" t="n">
+        <v>15</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -37526,10 +37506,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F495" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F495" t="n">
+        <v>5</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -37603,10 +37581,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F496" t="n">
+        <v>16</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -37680,10 +37656,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F497" t="n">
+        <v>10</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -37757,10 +37731,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F498" t="n">
+        <v>7</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
@@ -37834,10 +37806,8 @@
           <t>22/10/2026 a las 13:06</t>
         </is>
       </c>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F499" t="n">
+        <v>8</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -37911,10 +37881,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F500" t="n">
+        <v>5</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -37988,10 +37956,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F501" t="n">
+        <v>21</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -38065,10 +38031,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F502" t="n">
+        <v>11</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
@@ -38142,10 +38106,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F503" t="n">
+        <v>9</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
@@ -38219,10 +38181,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F504" t="n">
+        <v>14</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
@@ -38296,10 +38256,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F505" t="n">
+        <v>13</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
@@ -38373,10 +38331,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F506" t="n">
+        <v>19</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
@@ -38450,10 +38406,8 @@
           <t>22/10/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F507" t="n">
+        <v>12</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
@@ -38527,10 +38481,8 @@
           <t>22/10/2026 a las 13:14</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F508" t="n">
+        <v>21</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
@@ -38573,6 +38525,160 @@
         </is>
       </c>
       <c r="O508" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>24/10/2026 a las 12:11</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>C. E. R. EL CARMELO</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PEDRERA</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>VDA LA PEDRERA</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA PEDRERA</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>24/10/2026 a las 12:11</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>I. E. PUERTO VENUS</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>C. E. R. AGUACATAL</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>VDA. AGUACATAL</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>ón: VDA AGUACATAL</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O510"/>
+  <dimension ref="A1:O519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38556,10 +38556,8 @@
           <t>24/10/2026 a las 12:11</t>
         </is>
       </c>
-      <c r="F509" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="F509" t="n">
+        <v>68</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
@@ -38633,10 +38631,8 @@
           <t>24/10/2026 a las 12:11</t>
         </is>
       </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F510" t="n">
+        <v>10</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
@@ -38679,6 +38675,699 @@
         </is>
       </c>
       <c r="O510" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>I. E. R. ADOLFO MORENO USUGA</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>C. E. R. BUENAVISTA</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>VDA. BUENAVISTA</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>ón: VDA. BUENAVISTA</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>I. E. R. EL JUNCO</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>C. E. R. TENDIDOS</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>VDA. LOS TENDIDOS</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS TENDIDOS</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>I. E. R. EL HATO</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>I. E. R. LOS PINOS</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>VDA LOS PINOS</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>ón: VDA LOS PINOS</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>I. E. R. EL JUNCO</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>I. E. R. EL ORO</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>CORREG EL ORO</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>ón: CORREG EL ORO</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>E U EDUARDO CORREA</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Dirección: IND BRR EDUARDO CORREA</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>ón: IND BRR EDUARDO CORREA</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CRUZADA</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>C. E. R. CARRIZAL</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>VDA. CARRIZAL</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>ón: VDA CARRIZAL</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>I. E. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>I. E. PUEBLO NUEVO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>BR PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>ón: KR 30 25 A 12</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Puerto Berrío</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Puerto Berrio</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>I. E. BOMBONA</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>E U LA ISLA</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>B. PUERTO COLOMBIA</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>ón: KR 3 62 04</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>29/10/2026 a las 16:08</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>C. E. R. UVITAL</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>C. E. R. BERLIN</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>VDA. BERLIN</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>ón: VDA. BERLIN</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O519"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38706,10 +38706,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="F511" t="n">
+        <v>35</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -38783,10 +38781,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="F512" t="n">
+        <v>35</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
@@ -38860,10 +38856,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F513" t="n">
+        <v>21</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
@@ -38937,10 +38931,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F514" t="n">
+        <v>28</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
@@ -39014,10 +39006,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="F515" t="n">
+        <v>43</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
@@ -39091,10 +39081,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="F516" t="n">
+        <v>34</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
@@ -39168,10 +39156,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="F517" t="n">
+        <v>48</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
@@ -39245,10 +39231,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="F518" t="n">
+        <v>38</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
@@ -39322,10 +39306,8 @@
           <t>29/10/2026 a las 16:08</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="F519" t="n">
+        <v>37</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -39368,6 +39350,160 @@
         </is>
       </c>
       <c r="O519" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>30/10/2026 a las 15:06</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>INST EDUC TRICENTENARIO</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>INST EDUC TRICENTENARIO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>Dirección: KR 63 A 94 A 629</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>ón: KR 63 A 94 A 629</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>30/10/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Sede La Esperanza</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Dirección: VDA LA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>ón: VDA LA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
         <is>
           <t>A</t>
         </is>
